--- a/Data/27/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FED7447-0B62-4884-BB76-266AEEA6A25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,7 +208,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699403</t>
+    <t>10699543</t>
   </si>
   <si>
     <t>Passed</t>
@@ -231,10 +217,10 @@
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>Tyree</t>
-  </si>
-  <si>
-    <t>GSKSK</t>
+    <t>Mrs</t>
+  </si>
+  <si>
+    <t>GSKSKk</t>
   </si>
   <si>
     <t>SLNameOne</t>
@@ -333,7 +319,7 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
-    <t>10006469A</t>
+    <t>10006501A</t>
   </si>
   <si>
     <t>BBVAESMM111</t>
@@ -354,13 +340,19 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>10699544</t>
+  </si>
+  <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
-    <t>Waldo</t>
-  </si>
-  <si>
-    <t>Auto 68144866</t>
+    <t>SchirRR</t>
+  </si>
+  <si>
+    <t>SLNameTwoo</t>
+  </si>
+  <si>
+    <t>Auto 28086090</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -385,113 +377,110 @@
 </t>
   </si>
   <si>
-    <t>10006470A</t>
+    <t>10006502A</t>
   </si>
   <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
-  </si>
-  <si>
-    <t>SLNameTWONew</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -525,13 +514,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,18 +534,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -566,19 +547,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -674,6 +651,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1008,9 +988,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="11.08984375" customWidth="1"/>
@@ -1090,7 +1070,7 @@
     <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1287,7 +1267,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
@@ -1322,8 +1302,8 @@
         <v>71</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-7</f>
-        <v>45798</v>
+        <f t="shared" ref="L2" si="0">TODAY()-7</f>
+        <v>45803</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>69</v>
@@ -1356,8 +1336,8 @@
         <v>71</v>
       </c>
       <c r="W2" s="18">
-        <f t="shared" ref="W2:W3" ca="1" si="1">TODAY()-7</f>
-        <v>45798</v>
+        <f t="shared" ref="W2" si="1">TODAY()-7</f>
+        <v>45803</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>77</v>
@@ -1387,8 +1367,8 @@
         <v>84</v>
       </c>
       <c r="AG2" s="24">
-        <f ca="1">TODAY()+365</f>
-        <v>46170</v>
+        <f>TODAY()+365</f>
+        <v>46175</v>
       </c>
       <c r="AH2" s="12" t="s">
         <v>85</v>
@@ -1409,8 +1389,8 @@
         <v>90</v>
       </c>
       <c r="AN2" s="26">
-        <f t="shared" ref="AN2:AN3" ca="1" si="2">TODAY()+7</f>
-        <v>45812</v>
+        <f t="shared" ref="AN2" si="2">TODAY()+7</f>
+        <v>45817</v>
       </c>
       <c r="AO2" s="14" t="s">
         <v>91</v>
@@ -1422,8 +1402,8 @@
         <v>93</v>
       </c>
       <c r="AR2" s="24">
-        <f t="shared" ref="AR2:AR3" ca="1" si="3">TODAY()+365</f>
-        <v>46170</v>
+        <f t="shared" ref="AR2" si="3">TODAY()+365</f>
+        <v>46175</v>
       </c>
       <c r="AS2" s="27" t="s">
         <v>91</v>
@@ -1459,7 +1439,7 @@
         <v>98</v>
       </c>
       <c r="BD2" s="31">
-        <v>281000757388</v>
+        <v>281000757497</v>
       </c>
       <c r="BE2" s="30" t="s">
         <v>69</v>
@@ -1489,23 +1469,27 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="8"/>
+      <c r="B3" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="D3" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>69</v>
@@ -1520,8 +1504,7 @@
         <v>71</v>
       </c>
       <c r="L3" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>45798</v>
+        <v>45800</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>69</v>
@@ -1532,8 +1515,8 @@
       <c r="O3" s="12">
         <v>44</v>
       </c>
-      <c r="P3" s="12" t="s">
-        <v>73</v>
+      <c r="P3" s="12">
+        <v>28013</v>
       </c>
       <c r="Q3" s="15" t="s">
         <v>74</v>
@@ -1554,23 +1537,22 @@
         <v>71</v>
       </c>
       <c r="W3" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>45798</v>
+        <v>45800</v>
       </c>
       <c r="X3" s="12" t="s">
         <v>77</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Z3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AB3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC3" s="22">
         <v>365</v>
@@ -1582,7 +1564,7 @@
         <v>83</v>
       </c>
       <c r="AF3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AG3" s="35" t="s">
         <v>78</v>
@@ -1591,23 +1573,22 @@
         <v>85</v>
       </c>
       <c r="AI3" s="25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AJ3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AK3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="AL3" s="16" t="s">
-        <v>116</v>
+      <c r="AL3" s="36" t="s">
+        <v>118</v>
       </c>
       <c r="AM3" s="26" t="s">
         <v>90</v>
       </c>
       <c r="AN3" s="26">
-        <f t="shared" ca="1" si="2"/>
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="AO3" s="14" t="s">
         <v>91</v>
@@ -1619,8 +1600,7 @@
         <v>93</v>
       </c>
       <c r="AR3" s="24">
-        <f t="shared" ca="1" si="3"/>
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="AS3" s="27" t="s">
         <v>91</v>
@@ -1643,8 +1623,8 @@
       <c r="AY3" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="AZ3" s="29" t="s">
-        <v>97</v>
+      <c r="AZ3" s="29">
+        <v>40844</v>
       </c>
       <c r="BA3" s="28" t="s">
         <v>69</v>
@@ -1656,7 +1636,7 @@
         <v>98</v>
       </c>
       <c r="BD3" s="31">
-        <v>281000757489</v>
+        <v>281000757498</v>
       </c>
       <c r="BE3" s="30" t="s">
         <v>69</v>
@@ -1665,7 +1645,7 @@
         <v>99</v>
       </c>
       <c r="BG3" s="32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BH3" s="30" t="s">
         <v>101</v>
@@ -1677,7 +1657,7 @@
         <v>103</v>
       </c>
       <c r="BK3" s="30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BL3" s="30">
         <v>36526</v>
@@ -1686,13 +1666,13 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="6"/>
       <c r="C4" s="8"/>
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="36"/>
+      <c r="F4" s="37"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -1747,13 +1727,13 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="8"/>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="36"/>
+      <c r="F5" s="37"/>
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
@@ -1809,13 +1789,13 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="36"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
@@ -1871,13 +1851,13 @@
       <c r="BL6" s="30"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
       <c r="C7" s="8"/>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="36"/>
+      <c r="F7" s="37"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
@@ -1932,13 +1912,13 @@
       <c r="BL7" s="30"/>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="8"/>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="36"/>
+      <c r="F8" s="37"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
@@ -1993,13 +1973,13 @@
       <c r="BL8" s="30"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="36"/>
+      <c r="F9" s="37"/>
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
@@ -2055,13 +2035,13 @@
       <c r="BL9" s="30"/>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="8"/>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="36"/>
+      <c r="F10" s="37"/>
       <c r="G10" s="10"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
@@ -2081,7 +2061,7 @@
       <c r="W10" s="18"/>
       <c r="X10" s="12"/>
       <c r="Y10" s="19"/>
-      <c r="AA10" s="37"/>
+      <c r="AA10" s="38"/>
       <c r="AC10" s="22"/>
       <c r="AE10" s="14"/>
       <c r="AG10" s="35"/>
@@ -2116,13 +2096,13 @@
       <c r="BL10" s="30"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
       <c r="C11" s="8"/>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="36"/>
+      <c r="F11" s="37"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
@@ -2177,13 +2157,13 @@
       <c r="BL11" s="30"/>
       <c r="BM11" s="30"/>
     </row>
-    <row r="12" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
       <c r="C12" s="8"/>
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="36"/>
+      <c r="F12" s="37"/>
       <c r="G12" s="10"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
@@ -2203,7 +2183,7 @@
       <c r="W12" s="18"/>
       <c r="X12" s="12"/>
       <c r="Y12" s="19"/>
-      <c r="Z12" s="38"/>
+      <c r="Z12" s="39"/>
       <c r="AA12" s="21"/>
       <c r="AC12" s="22"/>
       <c r="AE12" s="14"/>
@@ -2239,13 +2219,13 @@
       <c r="BL12" s="30"/>
       <c r="BM12" s="30"/>
     </row>
-    <row r="13" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
       <c r="C13" s="8"/>
       <c r="D13" s="9"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="36"/>
+      <c r="F13" s="37"/>
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
       <c r="I13" s="12"/>
@@ -2265,9 +2245,9 @@
       <c r="W13" s="18"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="19"/>
-      <c r="Z13" s="38"/>
+      <c r="Z13" s="39"/>
       <c r="AA13" s="21"/>
-      <c r="AB13" s="38"/>
+      <c r="AB13" s="39"/>
       <c r="AC13" s="22"/>
       <c r="AE13" s="14"/>
       <c r="AG13" s="35"/>
@@ -2302,80 +2282,80 @@
       <c r="BL13" s="30"/>
       <c r="BM13" s="30"/>
     </row>
-    <row r="14" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
       <c r="C14" s="8"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="36"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="37"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
       <c r="L14" s="18"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="41"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="42"/>
       <c r="P14" s="12"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="44"/>
-      <c r="U14" s="45"/>
-      <c r="V14" s="41"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="45"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="42"/>
       <c r="W14" s="18"/>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="46"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="47"/>
       <c r="Z14" s="35"/>
-      <c r="AA14" s="47"/>
+      <c r="AA14" s="48"/>
       <c r="AB14" s="35"/>
-      <c r="AC14" s="48"/>
+      <c r="AC14" s="49"/>
       <c r="AD14" s="35"/>
-      <c r="AE14" s="42"/>
+      <c r="AE14" s="43"/>
       <c r="AF14" s="35"/>
       <c r="AG14" s="35"/>
-      <c r="AH14" s="41"/>
+      <c r="AH14" s="42"/>
       <c r="AI14" s="25"/>
-      <c r="AJ14" s="49"/>
-      <c r="AK14" s="41"/>
-      <c r="AL14" s="44"/>
-      <c r="AM14" s="50"/>
-      <c r="AN14" s="50"/>
+      <c r="AJ14" s="50"/>
+      <c r="AK14" s="42"/>
+      <c r="AL14" s="45"/>
+      <c r="AM14" s="51"/>
+      <c r="AN14" s="51"/>
       <c r="AO14" s="14"/>
       <c r="AP14" s="15"/>
       <c r="AQ14" s="16"/>
       <c r="AR14" s="24"/>
-      <c r="AS14" s="51"/>
+      <c r="AS14" s="52"/>
       <c r="AT14" s="35"/>
       <c r="AU14" s="18"/>
-      <c r="AV14" s="52"/>
-      <c r="AW14" s="52"/>
-      <c r="AX14" s="52"/>
-      <c r="AY14" s="52"/>
-      <c r="AZ14" s="53"/>
-      <c r="BA14" s="52"/>
-      <c r="BB14" s="54"/>
-      <c r="BC14" s="54"/>
+      <c r="AV14" s="53"/>
+      <c r="AW14" s="53"/>
+      <c r="AX14" s="53"/>
+      <c r="AY14" s="53"/>
+      <c r="AZ14" s="54"/>
+      <c r="BA14" s="53"/>
+      <c r="BB14" s="55"/>
+      <c r="BC14" s="55"/>
       <c r="BD14" s="31"/>
-      <c r="BE14" s="54"/>
-      <c r="BF14" s="54"/>
+      <c r="BE14" s="55"/>
+      <c r="BF14" s="55"/>
       <c r="BG14" s="32"/>
-      <c r="BH14" s="54"/>
-      <c r="BI14" s="54"/>
-      <c r="BJ14" s="54"/>
+      <c r="BH14" s="55"/>
+      <c r="BI14" s="55"/>
+      <c r="BJ14" s="55"/>
       <c r="BK14" s="30"/>
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
     </row>
-    <row r="15" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
       <c r="C15" s="8"/>
       <c r="D15" s="9"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="36"/>
+      <c r="F15" s="37"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -2431,13 +2411,13 @@
       <c r="BL15" s="30"/>
       <c r="BM15" s="30"/>
     </row>
-    <row r="16" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
       <c r="C16" s="8"/>
       <c r="D16" s="9"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="36"/>
+      <c r="F16" s="37"/>
       <c r="G16" s="10"/>
       <c r="H16" s="11"/>
       <c r="I16" s="12"/>
@@ -2457,7 +2437,7 @@
       <c r="W16" s="18"/>
       <c r="X16" s="12"/>
       <c r="Y16" s="19"/>
-      <c r="Z16" s="38"/>
+      <c r="Z16" s="39"/>
       <c r="AA16" s="21"/>
       <c r="AC16" s="22"/>
       <c r="AE16" s="14"/>
@@ -2493,9 +2473,9 @@
       <c r="BL16" s="30"/>
       <c r="BM16" s="30"/>
     </row>
-    <row r="17" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2575,7 +2555,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2655,7 +2635,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2735,7 +2715,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2815,7 +2795,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2895,7 +2875,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2975,7 +2955,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3055,7 +3035,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3135,7 +3115,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3215,7 +3195,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3295,7 +3275,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3375,7 +3355,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3455,7 +3435,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3535,7 +3515,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3615,7 +3595,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3695,7 +3675,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3775,7 +3755,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3855,7 +3835,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3935,7 +3915,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4015,7 +3995,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4095,7 +4075,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4175,7 +4155,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4255,7 +4235,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4335,7 +4315,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4415,7 +4395,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4495,7 +4475,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4575,7 +4555,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4655,7 +4635,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4735,7 +4715,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4815,7 +4795,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4895,7 +4875,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4975,7 +4955,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5055,7 +5035,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5135,7 +5115,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5215,7 +5195,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" spans="1:78" s="38" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5295,7 +5275,7 @@
       <c r="BY53" s="2"/>
       <c r="BZ53" s="2"/>
     </row>
-    <row r="54" spans="1:78" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5376,18 +5356,66 @@
       <c r="BZ54" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16 X10:X16 V10:V16 R10:S16 J10:K16 BI10:BI16 BC10:BC16 AY10:AY16 AP10:AP16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16 X2:X16 V2:V16 R2:S16 J2:K16 BI2:BI16 BC2:BC16 AY2:AY16 AP2:AP16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP10:AP16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2:AP16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY10:AY16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC10:BC16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI10:BI16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R10:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X10:X16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/27/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3AE886-5D98-4F77-9924-C0B72D1555D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="119">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -208,18 +222,9 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699543</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>Mrs</t>
-  </si>
-  <si>
     <t>GSKSKk</t>
   </si>
   <si>
@@ -319,9 +324,6 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
-    <t>10006501A</t>
-  </si>
-  <si>
     <t>BBVAESMM111</t>
   </si>
   <si>
@@ -338,9 +340,6 @@
   </si>
   <si>
     <t>Test_2</t>
-  </si>
-  <si>
-    <t>10699544</t>
   </si>
   <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
@@ -377,110 +376,119 @@
 </t>
   </si>
   <si>
-    <t>10006502A</t>
-  </si>
-  <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
+  </si>
+  <si>
+    <t>10006512A</t>
+  </si>
+  <si>
+    <t>10006513A</t>
+  </si>
+  <si>
+    <t>NineJune</t>
+  </si>
+  <si>
+    <t>NineJuneTwetyFive</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color indexed="8"/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
-      <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -514,13 +522,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999816888943144"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -534,10 +542,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -547,8 +563,12 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -988,9 +1008,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="11.08984375" customWidth="1"/>
@@ -1070,7 +1090,7 @@
     <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1267,250 +1287,242 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="I2" s="12">
         <v>919193394</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" ref="L2" si="0">TODAY()-7</f>
-        <v>45803</v>
+        <f t="shared" ref="L2" ca="1" si="0">TODAY()-7</f>
+        <v>45810</v>
       </c>
       <c r="M2" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" s="15" t="s">
         <v>69</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>72</v>
       </c>
       <c r="O2" s="12">
         <v>44</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="U2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="V2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="W2" s="18">
+        <f t="shared" ref="W2" ca="1" si="1">TODAY()-7</f>
+        <v>45810</v>
+      </c>
+      <c r="X2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="T2" s="16" t="s">
+      <c r="Y2" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="U2" s="17" t="s">
+      <c r="Z2" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="V2" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="W2" s="18">
-        <f t="shared" ref="W2" si="1">TODAY()-7</f>
-        <v>45803</v>
-      </c>
-      <c r="X2" s="12" t="s">
+      <c r="AA2" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="AB2" t="s">
         <v>78</v>
-      </c>
-      <c r="Z2" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA2" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>81</v>
       </c>
       <c r="AC2" s="22">
         <v>356</v>
       </c>
       <c r="AD2" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG2" s="24">
+        <f ca="1">TODAY()+365</f>
+        <v>46182</v>
+      </c>
+      <c r="AH2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AI2" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AJ2" t="s">
         <v>84</v>
       </c>
-      <c r="AG2" s="24">
-        <f>TODAY()+365</f>
-        <v>46175</v>
-      </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AK2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="AI2" s="25" t="s">
+      <c r="AL2" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AM2" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AN2" s="26">
+        <f t="shared" ref="AN2" ca="1" si="2">TODAY()+7</f>
+        <v>45824</v>
+      </c>
+      <c r="AO2" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="AL2" s="16" t="s">
+      <c r="AP2" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="AM2" s="26" t="s">
+      <c r="AQ2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AN2" s="26">
-        <f t="shared" ref="AN2" si="2">TODAY()+7</f>
-        <v>45817</v>
-      </c>
-      <c r="AO2" s="14" t="s">
+      <c r="AR2" s="24">
+        <f t="shared" ref="AR2" ca="1" si="3">TODAY()+365</f>
+        <v>46182</v>
+      </c>
+      <c r="AS2" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" t="s">
         <v>91</v>
-      </c>
-      <c r="AP2" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ2" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="AR2" s="24">
-        <f t="shared" ref="AR2" si="3">TODAY()+365</f>
-        <v>46175</v>
-      </c>
-      <c r="AS2" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>94</v>
       </c>
       <c r="AU2" s="13">
         <v>29221</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AW2" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX2" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="AY2" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="AZ2" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="BA2" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="BC2" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AX2" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY2" s="28" t="s">
+      <c r="BD2" s="31">
+        <v>281000757500</v>
+      </c>
+      <c r="BE2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF2" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" s="29" t="s">
+      <c r="BG2" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="BH2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC2" s="30" t="s">
+      <c r="BI2" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="BD2" s="31">
-        <v>281000757497</v>
-      </c>
-      <c r="BE2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF2" s="30" t="s">
+      <c r="BJ2" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="BG2" s="32" t="s">
+      <c r="BK2" s="30" t="s">
         <v>100</v>
-      </c>
-      <c r="BH2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="BI2" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="BJ2" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="BK2" s="30" t="s">
-        <v>104</v>
       </c>
       <c r="BL2" s="30">
         <v>36526</v>
       </c>
       <c r="BM2" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="3" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="I3" s="12">
         <v>919193436</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L3" s="13">
         <v>45800</v>
       </c>
       <c r="M3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" s="15" t="s">
         <v>69</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>72</v>
       </c>
       <c r="O3" s="12">
         <v>44</v>
@@ -1519,40 +1531,40 @@
         <v>28013</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="U3" s="15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W3" s="18">
         <v>45800</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="Z3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AC3" s="22">
         <v>365</v>
@@ -1561,112 +1573,112 @@
         <v>100</v>
       </c>
       <c r="AE3" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AG3" s="35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AH3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI3" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="AI3" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AK3" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="AL3" s="36" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="AM3" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AN3" s="26">
         <v>45814</v>
       </c>
       <c r="AO3" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AP3" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AQ3" s="16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AR3" s="24">
         <v>46172</v>
       </c>
       <c r="AS3" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT3" t="s">
         <v>91</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>94</v>
       </c>
       <c r="AU3" s="13">
         <v>29221</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AW3" s="28" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AX3" s="28" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AY3" s="28" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AZ3" s="29">
         <v>40844</v>
       </c>
       <c r="BA3" s="28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="BC3" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD3" s="31">
+        <v>281000757501</v>
+      </c>
+      <c r="BE3" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF3" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="BG3" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="BH3" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="BI3" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="BD3" s="31">
-        <v>281000757498</v>
-      </c>
-      <c r="BE3" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF3" s="30" t="s">
+      <c r="BJ3" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="BG3" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="BH3" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="BI3" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="BJ3" s="30" t="s">
-        <v>103</v>
-      </c>
       <c r="BK3" s="30" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="BL3" s="30">
         <v>36526</v>
       </c>
       <c r="BM3" s="30" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="4" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="6"/>
       <c r="C4" s="8"/>
@@ -1727,7 +1739,7 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="8"/>
@@ -1789,7 +1801,7 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
       <c r="C6" s="8"/>
@@ -1851,7 +1863,7 @@
       <c r="BL6" s="30"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
       <c r="C7" s="8"/>
@@ -1912,7 +1924,7 @@
       <c r="BL7" s="30"/>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="8"/>
@@ -1973,7 +1985,7 @@
       <c r="BL8" s="30"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
       <c r="C9" s="8"/>
@@ -2035,7 +2047,7 @@
       <c r="BL9" s="30"/>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="8"/>
@@ -2096,7 +2108,7 @@
       <c r="BL10" s="30"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
       <c r="C11" s="8"/>
@@ -2157,7 +2169,7 @@
       <c r="BL11" s="30"/>
       <c r="BM11" s="30"/>
     </row>
-    <row r="12" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
       <c r="C12" s="8"/>
@@ -2219,7 +2231,7 @@
       <c r="BL12" s="30"/>
       <c r="BM12" s="30"/>
     </row>
-    <row r="13" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
       <c r="C13" s="8"/>
@@ -2282,7 +2294,7 @@
       <c r="BL13" s="30"/>
       <c r="BM13" s="30"/>
     </row>
-    <row r="14" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
       <c r="C14" s="8"/>
@@ -2349,7 +2361,7 @@
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
     </row>
-    <row r="15" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
       <c r="C15" s="8"/>
@@ -2411,7 +2423,7 @@
       <c r="BL15" s="30"/>
       <c r="BM15" s="30"/>
     </row>
-    <row r="16" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
       <c r="C16" s="8"/>
@@ -2473,9 +2485,9 @@
       <c r="BL16" s="30"/>
       <c r="BM16" s="30"/>
     </row>
-    <row r="17" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2555,7 +2567,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2635,7 +2647,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2715,7 +2727,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2795,7 +2807,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2875,7 +2887,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2955,7 +2967,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3035,7 +3047,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3115,7 +3127,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3195,7 +3207,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3275,7 +3287,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3355,7 +3367,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3435,7 +3447,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3515,7 +3527,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3595,7 +3607,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3675,7 +3687,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3755,7 +3767,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3835,7 +3847,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3915,7 +3927,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3995,7 +4007,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4075,7 +4087,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4155,7 +4167,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4235,7 +4247,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4315,7 +4327,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4395,7 +4407,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4475,7 +4487,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4555,7 +4567,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4635,7 +4647,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4715,7 +4727,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4795,7 +4807,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4875,7 +4887,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4955,7 +4967,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5035,7 +5047,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5115,7 +5127,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5195,7 +5207,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5275,7 +5287,7 @@
       <c r="BY53" s="2"/>
       <c r="BZ53" s="2"/>
     </row>
-    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:78" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5356,66 +5368,18 @@
       <c r="BZ54" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="18">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16 X10:X16 V10:V16 R10:S16 J10:K16 BI10:BI16 BC10:BC16 AY10:AY16 AP10:AP16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP10:AP16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2:AP16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY10:AY16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC10:BC16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI10:BI16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:K16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R10:S16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:S16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X10:X16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16 X2:X16 V2:V16 R2:S16 J2:K16 BI2:BI16 BC2:BC16 AY2:AY16 AP2:AP16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/27/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3AE886-5D98-4F77-9924-C0B72D1555D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,13 +208,22 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>10699765</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>GSKSKk</t>
-  </si>
-  <si>
-    <t>SLNameOne</t>
+    <t>TwentyJune</t>
+  </si>
+  <si>
+    <t>GSK</t>
+  </si>
+  <si>
+    <t>NewOne</t>
   </si>
   <si>
     <t>Spain</t>
@@ -324,6 +319,9 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
+    <t>10006525A</t>
+  </si>
+  <si>
     <t>BBVAESMM111</t>
   </si>
   <si>
@@ -345,13 +343,16 @@
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
+    <t>EighteenJune</t>
+  </si>
+  <si>
     <t>SchirRR</t>
   </si>
   <si>
     <t>SLNameTwoo</t>
   </si>
   <si>
-    <t>Auto 28086090</t>
+    <t>Auto 8092876</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -376,119 +377,110 @@
 </t>
   </si>
   <si>
+    <t>10006514A</t>
+  </si>
+  <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
-  </si>
-  <si>
-    <t>10006512A</t>
-  </si>
-  <si>
-    <t>10006513A</t>
-  </si>
-  <si>
-    <t>NineJune</t>
-  </si>
-  <si>
-    <t>NineJuneTwetyFive</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -522,13 +514,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,18 +534,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -563,12 +547,8 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -1008,12 +988,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="51.36328125" customWidth="1"/>
     <col min="3" max="3" width="10.1796875" customWidth="1"/>
     <col min="4" max="4" width="41.453125" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
@@ -1090,7 +1070,7 @@
     <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1287,242 +1267,250 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="D2" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I2" s="12">
         <v>919193394</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" ref="L2" ca="1" si="0">TODAY()-7</f>
-        <v>45810</v>
+        <f t="shared" ref="L2" si="0">TODAY()-7</f>
+        <v>45820</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O2" s="12">
         <v>44</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="S2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="T2" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="V2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="S2" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T2" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="V2" s="12" t="s">
-        <v>68</v>
-      </c>
       <c r="W2" s="18">
-        <f t="shared" ref="W2" ca="1" si="1">TODAY()-7</f>
-        <v>45810</v>
+        <f t="shared" ref="W2" si="1">TODAY()-7</f>
+        <v>45820</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Y2" s="19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Z2" s="20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AA2" s="21" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AC2" s="22">
         <v>356</v>
       </c>
       <c r="AD2" s="23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AE2" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AF2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AG2" s="24">
-        <f ca="1">TODAY()+365</f>
-        <v>46182</v>
+        <f>TODAY()+365</f>
+        <v>46192</v>
       </c>
       <c r="AH2" s="12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AI2" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AJ2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AK2" s="12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AL2" s="16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM2" s="26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AN2" s="26">
-        <f t="shared" ref="AN2" ca="1" si="2">TODAY()+7</f>
-        <v>45824</v>
+        <f t="shared" ref="AN2" si="2">TODAY()+7</f>
+        <v>45834</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AP2" s="15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AQ2" s="16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AR2" s="24">
-        <f t="shared" ref="AR2" ca="1" si="3">TODAY()+365</f>
-        <v>46182</v>
+        <f t="shared" ref="AR2" si="3">TODAY()+365</f>
+        <v>46192</v>
       </c>
       <c r="AS2" s="27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AT2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AU2" s="13">
         <v>29221</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AW2" s="28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AX2" s="28" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AY2" s="28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AZ2" s="29" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="BA2" s="28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BB2" s="30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BC2" s="30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="BD2" s="31">
-        <v>281000757500</v>
+        <v>281000757510</v>
       </c>
       <c r="BE2" s="30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BF2" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="BG2" s="32" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="BH2" s="30" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="BI2" s="30" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="BJ2" s="30" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="BK2" s="30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="BL2" s="30">
         <v>36526</v>
       </c>
       <c r="BM2" s="30" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="8"/>
+        <v>106</v>
+      </c>
+      <c r="B3" s="34">
+        <v>10699752</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="D3" s="9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I3" s="12">
         <v>919193436</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L3" s="13">
         <v>45800</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O3" s="12">
         <v>44</v>
@@ -1531,40 +1519,40 @@
         <v>28013</v>
       </c>
       <c r="Q3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="S3" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="T3" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="V3" s="12" t="s">
         <v>71</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="V3" s="12" t="s">
-        <v>68</v>
       </c>
       <c r="W3" s="18">
         <v>45800</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Z3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AB3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="AC3" s="22">
         <v>365</v>
@@ -1573,112 +1561,112 @@
         <v>100</v>
       </c>
       <c r="AE3" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="AG3" s="35" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AH3" s="12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AI3" s="25" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="AJ3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AK3" s="12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AL3" s="36" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AM3" s="26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AN3" s="26">
         <v>45814</v>
       </c>
       <c r="AO3" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AP3" s="15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AQ3" s="16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AR3" s="24">
         <v>46172</v>
       </c>
       <c r="AS3" s="27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AT3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AU3" s="13">
         <v>29221</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AW3" s="28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AX3" s="28" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AY3" s="28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AZ3" s="29">
         <v>40844</v>
       </c>
       <c r="BA3" s="28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BC3" s="30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="BD3" s="31">
-        <v>281000757501</v>
+        <v>281000757503</v>
       </c>
       <c r="BE3" s="30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BF3" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="BG3" s="32" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BH3" s="30" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="BI3" s="30" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="BJ3" s="30" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="BK3" s="30" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="BL3" s="30">
         <v>36526</v>
       </c>
       <c r="BM3" s="30" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="6"/>
       <c r="C4" s="8"/>
@@ -1739,7 +1727,7 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="8"/>
@@ -1801,7 +1789,7 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
       <c r="C6" s="8"/>
@@ -1863,7 +1851,7 @@
       <c r="BL6" s="30"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
       <c r="C7" s="8"/>
@@ -1924,7 +1912,7 @@
       <c r="BL7" s="30"/>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="8"/>
@@ -1985,7 +1973,7 @@
       <c r="BL8" s="30"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
       <c r="C9" s="8"/>
@@ -2047,7 +2035,7 @@
       <c r="BL9" s="30"/>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="8"/>
@@ -2108,7 +2096,7 @@
       <c r="BL10" s="30"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
       <c r="C11" s="8"/>
@@ -2169,7 +2157,7 @@
       <c r="BL11" s="30"/>
       <c r="BM11" s="30"/>
     </row>
-    <row r="12" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
       <c r="C12" s="8"/>
@@ -2231,7 +2219,7 @@
       <c r="BL12" s="30"/>
       <c r="BM12" s="30"/>
     </row>
-    <row r="13" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
       <c r="C13" s="8"/>
@@ -2294,7 +2282,7 @@
       <c r="BL13" s="30"/>
       <c r="BM13" s="30"/>
     </row>
-    <row r="14" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
       <c r="C14" s="8"/>
@@ -2361,7 +2349,7 @@
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
     </row>
-    <row r="15" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
       <c r="C15" s="8"/>
@@ -2423,7 +2411,7 @@
       <c r="BL15" s="30"/>
       <c r="BM15" s="30"/>
     </row>
-    <row r="16" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
       <c r="C16" s="8"/>
@@ -2485,9 +2473,9 @@
       <c r="BL16" s="30"/>
       <c r="BM16" s="30"/>
     </row>
-    <row r="17" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2567,7 +2555,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2647,7 +2635,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2727,7 +2715,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2807,7 +2795,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2887,7 +2875,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2967,7 +2955,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3047,7 +3035,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3127,7 +3115,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3207,7 +3195,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3287,7 +3275,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3367,7 +3355,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3447,7 +3435,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3527,7 +3515,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3607,7 +3595,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3687,7 +3675,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3767,7 +3755,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3847,7 +3835,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3927,7 +3915,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4007,7 +3995,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4087,7 +4075,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4167,7 +4155,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4247,7 +4235,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4327,7 +4315,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4407,7 +4395,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4487,7 +4475,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4567,7 +4555,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4647,7 +4635,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4727,7 +4715,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4807,7 +4795,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4887,7 +4875,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4967,7 +4955,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5047,7 +5035,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5127,7 +5115,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5207,7 +5195,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" spans="1:78" s="39" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5287,7 +5275,7 @@
       <c r="BY53" s="2"/>
       <c r="BZ53" s="2"/>
     </row>
-    <row r="54" spans="1:78" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5368,18 +5356,66 @@
       <c r="BZ54" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16 X10:X16 V10:V16 R10:S16 J10:K16 BI10:BI16 BC10:BC16 AY10:AY16 AP10:AP16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16 X2:X16 V2:V16 R2:S16 J2:K16 BI2:BI16 BC2:BC16 AY2:AY16 AP2:AP16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP10:AP16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2:AP16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY10:AY16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC10:BC16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI10:BI16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R10:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X10:X16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>